--- a/supabase/templates/template_tenants.xlsx
+++ b/supabase/templates/template_tenants.xlsx
@@ -397,13 +397,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:N3"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
     <col min="3" max="3" width="18.83203125" customWidth="1"/>
     <col min="4" max="4" width="18.83203125" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+    <col min="10" max="10" width="18.83203125" customWidth="1"/>
+    <col min="11" max="11" width="18.83203125" customWidth="1"/>
+    <col min="12" max="12" width="18.83203125" customWidth="1"/>
+    <col min="13" max="13" width="18.83203125" customWidth="1"/>
+    <col min="14" max="14" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -417,10 +426,37 @@
         <v>رقم الهوية</v>
       </c>
       <c r="D1" t="str">
+        <v>رقم الإقامة</v>
+      </c>
+      <c r="E1" t="str">
+        <v>رقم الجواز</v>
+      </c>
+      <c r="F1" t="str">
         <v>الجوال</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>البريد الإلكتروني</v>
+      </c>
+      <c r="H1" t="str">
+        <v>الرقم الموحد</v>
+      </c>
+      <c r="I1" t="str">
+        <v>السجل التجاري</v>
+      </c>
+      <c r="J1" t="str">
+        <v>الرقم الضريبي</v>
+      </c>
+      <c r="K1" t="str">
+        <v>اسم الممثل</v>
+      </c>
+      <c r="L1" t="str">
+        <v>رقم هوية الممثل</v>
+      </c>
+      <c r="M1" t="str">
+        <v>صفة الممثل</v>
+      </c>
+      <c r="N1" t="str">
+        <v>جوال الممثل</v>
       </c>
     </row>
     <row r="2">
@@ -431,18 +467,89 @@
         <v>فرد</v>
       </c>
       <c r="C2" t="str">
-        <v>2087654321</v>
+        <v>1087654321</v>
       </c>
       <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
         <v>0559876543</v>
       </c>
-      <c r="E2" t="str">
+      <c r="G2" t="str">
         <v>ahmad@example.com</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>شركة الريان التجارية</v>
+      </c>
+      <c r="B3" t="str">
+        <v>شركة</v>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>0551112222</v>
+      </c>
+      <c r="G3" t="str">
+        <v>info@rayan.example</v>
+      </c>
+      <c r="H3" t="str">
+        <v>7001234567</v>
+      </c>
+      <c r="I3" t="str">
+        <v>1010101010</v>
+      </c>
+      <c r="J3" t="str">
+        <v>300000000000003</v>
+      </c>
+      <c r="K3" t="str">
+        <v>خالد الريان</v>
+      </c>
+      <c r="L3" t="str">
+        <v>1090909090</v>
+      </c>
+      <c r="M3" t="str">
+        <v>مدير عام</v>
+      </c>
+      <c r="N3" t="str">
+        <v>0553334444</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N3"/>
   </ignoredErrors>
 </worksheet>
 </file>